--- a/new-info18/web.xlsx
+++ b/new-info18/web.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17025" windowHeight="10470"/>
+    <workbookView windowWidth="16245" windowHeight="11745"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet3" sheetId="14" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="13" r:id="rId2"/>
-    <sheet name="Sheet5" sheetId="10" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="15" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="16" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="54">
   <si>
     <t>domain</t>
   </si>
@@ -40,85 +46,157 @@
     <t>color2</t>
   </si>
   <si>
-    <t>zonates.cloud</t>
-  </si>
-  <si>
-    <t>#92cff4</t>
-  </si>
-  <si>
-    <t>bipinnates.cloud</t>
-  </si>
-  <si>
-    <t>#ba7ac7</t>
-  </si>
-  <si>
-    <t>ypsiliforms.cloud</t>
-  </si>
-  <si>
-    <t>#8cd1bc</t>
-  </si>
-  <si>
-    <t>lorimers.top</t>
-  </si>
-  <si>
-    <t>#8bbb6a</t>
-  </si>
-  <si>
-    <t>camesiot.top</t>
-  </si>
-  <si>
-    <t>#70c588</t>
-  </si>
-  <si>
-    <t>studiositys.site</t>
-  </si>
-  <si>
-    <t>lotics.site</t>
-  </si>
-  <si>
-    <t>mokes.site</t>
-  </si>
-  <si>
-    <t>funicles.site</t>
-  </si>
-  <si>
-    <t>whorls.cloud</t>
-  </si>
-  <si>
-    <t>conatuss.top</t>
-  </si>
-  <si>
-    <t>#e2e1dd</t>
-  </si>
-  <si>
-    <t>#8abe98</t>
-  </si>
-  <si>
-    <t>droshky.fun</t>
-  </si>
-  <si>
-    <t>#fafbe6</t>
-  </si>
-  <si>
-    <t>#a48ce6</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#c6e6e8</t>
-  </si>
-  <si>
-    <t>#373834</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#e3e3e5</t>
-  </si>
-  <si>
-    <t>#707899</t>
+    <t>date</t>
+  </si>
+  <si>
+    <t>read.finotide.com</t>
+  </si>
+  <si>
+    <t>#606da1</t>
+  </si>
+  <si>
+    <t>#fb9966</t>
+  </si>
+  <si>
+    <t>sec.finotide.com</t>
+  </si>
+  <si>
+    <t>#e6e3c3</t>
+  </si>
+  <si>
+    <t>#a7dbc8</t>
+  </si>
+  <si>
+    <t>#6b496a</t>
+  </si>
+  <si>
+    <t>#ddd23b</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>play.gravelcover.cloud</t>
+  </si>
+  <si>
+    <t>#ffb400</t>
+  </si>
+  <si>
+    <t>sec.gravelcover.cloud</t>
+  </si>
+  <si>
+    <t>#008fbd</t>
+  </si>
+  <si>
+    <t>template</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>game53</t>
+  </si>
+  <si>
+    <t>play.roadoffset.cloud</t>
+  </si>
+  <si>
+    <t>#1c579b</t>
+  </si>
+  <si>
+    <t>sec.roadoffset.cloud</t>
+  </si>
+  <si>
+    <t>#003153</t>
+  </si>
+  <si>
+    <t>play.frontages.site</t>
+  </si>
+  <si>
+    <t>#dfbc1f</t>
+  </si>
+  <si>
+    <t>sec.frontages.site</t>
+  </si>
+  <si>
+    <t>#284fef</t>
+  </si>
+  <si>
+    <t>game18</t>
+  </si>
+  <si>
+    <t>play.medianbar.fun</t>
+  </si>
+  <si>
+    <t>#ddbb99</t>
+  </si>
+  <si>
+    <t>sec.medianbar.fun</t>
+  </si>
+  <si>
+    <t>#b65458</t>
+  </si>
+  <si>
+    <t>game28</t>
+  </si>
+  <si>
+    <t>play.sunseabc.com</t>
+  </si>
+  <si>
+    <t>#f53d93</t>
+  </si>
+  <si>
+    <t>sec.sunseabc.com</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>周一</t>
+  </si>
+  <si>
+    <t>周二</t>
+  </si>
+  <si>
+    <t>周三</t>
+  </si>
+  <si>
+    <t>周四</t>
+  </si>
+  <si>
+    <t>周五</t>
+  </si>
+  <si>
+    <t>周六</t>
+  </si>
+  <si>
+    <t>周日</t>
+  </si>
+  <si>
+    <t>早餐</t>
+  </si>
+  <si>
+    <t>板栗</t>
+  </si>
+  <si>
+    <t>午餐</t>
+  </si>
+  <si>
+    <t>意面+生菜+鸡胸肉丸</t>
+  </si>
+  <si>
+    <t>晚餐</t>
+  </si>
+  <si>
+    <t>一个鸡蛋，一根玉米</t>
+  </si>
+  <si>
+    <t>havenlyspaces.net</t>
+  </si>
+  <si>
+    <t>adcloud-culture.com</t>
   </si>
 </sst>
 </file>
@@ -131,7 +209,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="33">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -140,9 +218,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -155,18 +262,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -320,7 +455,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,43 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E1DD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ABE98"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA48CE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E6E8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF373834"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3E3E5"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C579B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,31 +482,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92CFF4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA7AC7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8CD1BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BBB6A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C588"/>
+        <fgColor rgb="FF003153"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFBC1F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE58889"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF284FEF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDBB99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB65458"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF53D93"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB400"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF008FBD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF606DA1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFB9966"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6E3C3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6B496A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD23B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,199 +866,251 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -949,6 +1166,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <mruColors>
+      <color rgb="00F4F207"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1279,13 +1501,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="4" max="4" width="9.25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1295,54 +1518,236 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="11" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="12" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="29" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="11" t="s">
+      <c r="B2" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C2" s="31" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="11" t="s">
+      <c r="D2" s="13">
+        <v>46266</v>
+      </c>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B3" s="32" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="11" t="s">
+      <c r="C3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D3" s="13">
+        <v>46293</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="28"/>
+      <c r="B4" s="34" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="11" t="s">
+      <c r="C4" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>12</v>
-      </c>
+      <c r="D4" s="28"/>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="36"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="zonates.cloud"/>
-    <hyperlink ref="A3" r:id="rId2" display="bipinnates.cloud"/>
-    <hyperlink ref="A4" r:id="rId3" display="ypsiliforms.cloud"/>
-    <hyperlink ref="A5" r:id="rId4" display="lorimers.top"/>
-    <hyperlink ref="A6" r:id="rId5" display="camesiot.top"/>
+    <hyperlink ref="A10" r:id="rId1"/>
+    <hyperlink ref="A11" r:id="rId2"/>
+    <hyperlink ref="A2" r:id="rId3" display="read.finotide.com" tooltip="https://finotide.com"/>
+    <hyperlink ref="A3" r:id="rId3" display="sec.finotide.com" tooltip="https://finotide.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1352,10 +1757,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="26.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1365,54 +1773,86 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="11" t="s">
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="12" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="14">
+        <v>3</v>
+      </c>
+      <c r="E2" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="E3" s="14">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>12</v>
-      </c>
+    <row r="4" spans="1:6">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="28"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="28"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="28"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="28"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="28"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="studiositys.site"/>
-    <hyperlink ref="A3" r:id="rId2" display="lotics.site"/>
-    <hyperlink ref="A4" r:id="rId3" display="mokes.site"/>
-    <hyperlink ref="A5" r:id="rId4" display="funicles.site"/>
-    <hyperlink ref="A6" r:id="rId5" display="whorls.cloud"/>
+    <hyperlink ref="A6" r:id="rId1" tooltip="https://reededfluting.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1422,87 +1862,437 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="17.75" customWidth="1"/>
+    <col min="2" max="2" width="27.75" customWidth="1"/>
+    <col min="5" max="5" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="14">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G2" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="G3" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:9">
+      <c r="A4" s="9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14">
+        <v>3</v>
+      </c>
+      <c r="G4" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14">
+        <v>4</v>
+      </c>
+      <c r="G5" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="B6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14">
+        <v>5</v>
+      </c>
+      <c r="G6" s="14">
+        <v>6</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="14">
+        <v>1</v>
+      </c>
+      <c r="G7" s="14">
+        <v>7</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14">
+        <v>2</v>
+      </c>
+      <c r="G8" s="14">
+        <v>7</v>
+      </c>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="14">
+        <v>3</v>
+      </c>
+      <c r="G9" s="14">
+        <v>7</v>
+      </c>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="25"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="E21" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1"/>
-    <hyperlink ref="A2" r:id="rId2" display="conatuss.top"/>
-    <hyperlink ref="A3" r:id="rId3" display="droshky.fun"/>
-    <hyperlink ref="A4" r:id="rId4" display="spuddles.fun"/>
-    <hyperlink ref="A5" r:id="rId5" display="moilfuns.fun"/>
+    <hyperlink ref="G16" r:id="rId1"/>
+    <hyperlink ref="G17" r:id="rId2"/>
+    <hyperlink ref="B8" r:id="rId3" display="play.sunseabc.com"/>
+    <hyperlink ref="B9" r:id="rId3" display="sec.sunseabc.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <cols>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="22.375" customWidth="1"/>
+    <col min="5" max="5" width="22.625" customWidth="1"/>
+    <col min="6" max="6" width="24.25" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="1:8">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" ht="52" customHeight="1" spans="1:8">
+      <c r="A3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" ht="74" customHeight="1" spans="1:8">
+      <c r="A4" s="4"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" ht="100" customHeight="1" spans="1:8">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="C11" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:A4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>